--- a/tame_output/ON/bt/strategyON_20240202.xlsx
+++ b/tame_output/ON/bt/strategyON_20240202.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.4%</t>
+          <t>451.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.4%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1860"/>
+  <dimension ref="A1:G1861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.283988034426075</v>
+        <v>3.284619513310985</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44341,6 +44341,29 @@
       </c>
       <c r="G1860" t="n">
         <v>4.466850284015102</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B1861" t="n">
+        <v>3.307450549430455</v>
+      </c>
+      <c r="C1861" t="n">
+        <v>3.11093690068884</v>
+      </c>
+      <c r="D1861" t="n">
+        <v>1.641910514001567</v>
+      </c>
+      <c r="E1861" t="n">
+        <v>3.767344681975719</v>
+      </c>
+      <c r="F1861" t="n">
+        <v>2.257489958303713</v>
+      </c>
+      <c r="G1861" t="n">
+        <v>4.465430875671068</v>
       </c>
     </row>
   </sheetData>
